--- a/outputs/time_series_by_sensor/time_serie_sensorB-m10_p2.xlsx
+++ b/outputs/time_series_by_sensor/time_serie_sensorB-m10_p2.xlsx
@@ -1,37 +1,273 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="time_domain" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="time_domain" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>E2-Aluno1</t>
+  </si>
+  <si>
+    <t>E2-Aluno2</t>
+  </si>
+  <si>
+    <t>E2-Aluno3</t>
+  </si>
+  <si>
+    <t>E2-Aluno4</t>
+  </si>
+  <si>
+    <t>E2-Aluno5</t>
+  </si>
+  <si>
+    <t>sensorB-m10</t>
+  </si>
+  <si>
+    <t>15:20:58</t>
+  </si>
+  <si>
+    <t>15:20:59</t>
+  </si>
+  <si>
+    <t>15:21:00</t>
+  </si>
+  <si>
+    <t>15:21:01</t>
+  </si>
+  <si>
+    <t>15:21:02</t>
+  </si>
+  <si>
+    <t>15:21:03</t>
+  </si>
+  <si>
+    <t>15:21:04</t>
+  </si>
+  <si>
+    <t>15:21:05</t>
+  </si>
+  <si>
+    <t>15:21:06</t>
+  </si>
+  <si>
+    <t>15:21:07</t>
+  </si>
+  <si>
+    <t>15:21:08</t>
+  </si>
+  <si>
+    <t>15:21:09</t>
+  </si>
+  <si>
+    <t>15:21:10</t>
+  </si>
+  <si>
+    <t>15:21:11</t>
+  </si>
+  <si>
+    <t>15:21:12</t>
+  </si>
+  <si>
+    <t>15:21:13</t>
+  </si>
+  <si>
+    <t>15:21:14</t>
+  </si>
+  <si>
+    <t>15:21:15</t>
+  </si>
+  <si>
+    <t>15:21:16</t>
+  </si>
+  <si>
+    <t>15:21:17</t>
+  </si>
+  <si>
+    <t>15:21:18</t>
+  </si>
+  <si>
+    <t>15:21:19</t>
+  </si>
+  <si>
+    <t>15:21:20</t>
+  </si>
+  <si>
+    <t>15:21:21</t>
+  </si>
+  <si>
+    <t>15:21:22</t>
+  </si>
+  <si>
+    <t>15:21:23</t>
+  </si>
+  <si>
+    <t>15:21:24</t>
+  </si>
+  <si>
+    <t>15:21:25</t>
+  </si>
+  <si>
+    <t>15:21:26</t>
+  </si>
+  <si>
+    <t>15:21:27</t>
+  </si>
+  <si>
+    <t>15:21:28</t>
+  </si>
+  <si>
+    <t>15:21:29</t>
+  </si>
+  <si>
+    <t>15:21:30</t>
+  </si>
+  <si>
+    <t>15:21:31</t>
+  </si>
+  <si>
+    <t>15:21:32</t>
+  </si>
+  <si>
+    <t>15:21:33</t>
+  </si>
+  <si>
+    <t>15:21:34</t>
+  </si>
+  <si>
+    <t>15:21:35</t>
+  </si>
+  <si>
+    <t>15:21:36</t>
+  </si>
+  <si>
+    <t>15:21:37</t>
+  </si>
+  <si>
+    <t>15:21:38</t>
+  </si>
+  <si>
+    <t>15:21:39</t>
+  </si>
+  <si>
+    <t>15:21:40</t>
+  </si>
+  <si>
+    <t>15:21:41</t>
+  </si>
+  <si>
+    <t>15:21:42</t>
+  </si>
+  <si>
+    <t>15:21:43</t>
+  </si>
+  <si>
+    <t>15:21:44</t>
+  </si>
+  <si>
+    <t>15:21:45</t>
+  </si>
+  <si>
+    <t>15:21:46</t>
+  </si>
+  <si>
+    <t>15:21:47</t>
+  </si>
+  <si>
+    <t>15:21:48</t>
+  </si>
+  <si>
+    <t>15:21:49</t>
+  </si>
+  <si>
+    <t>15:21:50</t>
+  </si>
+  <si>
+    <t>15:21:51</t>
+  </si>
+  <si>
+    <t>15:21:52</t>
+  </si>
+  <si>
+    <t>15:21:53</t>
+  </si>
+  <si>
+    <t>15:21:54</t>
+  </si>
+  <si>
+    <t>15:21:55</t>
+  </si>
+  <si>
+    <t>15:21:56</t>
+  </si>
+  <si>
+    <t>15:21:57</t>
+  </si>
+  <si>
+    <t>15:21:58</t>
+  </si>
+  <si>
+    <t>15:21:59</t>
+  </si>
+  <si>
+    <t>15:22:00</t>
+  </si>
+  <si>
+    <t>15:22:01</t>
+  </si>
+  <si>
+    <t>15:22:02</t>
+  </si>
+  <si>
+    <t>15:22:03</t>
+  </si>
+  <si>
+    <t>15:22:04</t>
+  </si>
+  <si>
+    <t>15:22:05</t>
+  </si>
+  <si>
+    <t>15:22:06</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +282,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,1677 +598,1471 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G70"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>E2-Aluno1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E2-Aluno2</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>E2-Aluno3</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E2-Aluno4</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>E2-Aluno5</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>sensorB-m10</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>15:20:58</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2">
         <v>60.16842</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>15:20:59</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3">
         <v>55.220547</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>56.81797</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>55.7</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>15:21:00</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
         <v>53.9</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>54.583523</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>57.352875</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>60.921494</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>54.9</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>15:21:01</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
         <v>52.6</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>56.693806</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>55.039978</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>60.139248</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>51.8</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>15:21:02</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
         <v>51.4</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>55.44568</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>54.55189</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>50.4</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>56.35701</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>51.6</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>15:21:03</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
         <v>51.2</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>55.31684</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>53.958893</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>50.7</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>56.426994</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>51.7</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>15:21:04</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
         <v>51</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>54.923195</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>53.787716</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>51.1</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>56.2537</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>52.3</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>15:21:05</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
         <v>51.7</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>54.88875</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>54.81791</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>51.3</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>56.495636</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>52.2</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>15:21:06</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
         <v>51.4</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>55.52993</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>54.28296</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>50.7</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>56.96456</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>51.7</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>15:21:07</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
         <v>50.8</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>55.241035</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>54.108685</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>50.7</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>56.384747</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>51.2</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>15:21:08</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
         <v>50.4</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>55.1272</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>53.85573</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>49.6</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>56.842262</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>52.4</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>15:21:09</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
         <v>51.8</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>54.767345</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>54.307846</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>51.1</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>56.45578</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>52.7</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>15:21:10</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
         <v>51.4</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>56.31334</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>54.67422</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>51.1</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>57.458904</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>52.2</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>15:21:11</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15">
         <v>51.4</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>55.925724</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>54.31742</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>51.1</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>57.03365</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>51</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>15:21:12</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16">
         <v>50.4</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>55.44242</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>53.359833</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>50.2</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>56.169323</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>50.4</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>15:21:13</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17">
         <v>50</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>54.295918</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>53.185074</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>49.7</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>55.79084</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>50</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>15:21:14</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18">
         <v>49.8</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>54.07145</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>52.535572</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>49.5</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>55.449444</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>50.3</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>15:21:15</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19">
         <v>50.8</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>53.314713</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>52.16347</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>49.8</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>55.025646</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>50.4</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>15:21:16</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20">
         <v>49.3</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>53.46362</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>52.713642</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>49.5</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>55.28439</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>51.8</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>15:21:17</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21">
         <v>50.1</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>54.55057</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>54.069027</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>49.2</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>58.08797</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>50.1</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>15:21:18</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22">
         <v>50.4</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>54.128735</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>54.440937</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>49.5</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>55.098698</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>50.4</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>15:21:19</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23">
         <v>50.6</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>53.09369</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>52.822773</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>49.6</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>54.76502</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>52</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>15:21:20</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24">
         <v>52</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>52.844257</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>52.847343</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>51.3</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>54.73624</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>50.4</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>15:21:21</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25">
         <v>53.6</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>53.24364</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>53.156403</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>50.4</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>56.604137</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>49.6</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>15:21:22</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26">
         <v>49.6</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>52.870823</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>52.926212</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>51.3</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>55.59835</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>50.8</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>15:21:23</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27">
         <v>52.6</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>51.63481</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>52.737156</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>50.6</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>54.148903</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>52.4</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>15:21:24</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28">
         <v>53.8</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>52.993767</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>54.383705</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>53.6</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>56.45202</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28">
         <v>54</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>15:21:25</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29">
         <v>54.3</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>55.87796</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>56.747597</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>53.7</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>59.03038</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>54.8</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>15:21:26</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30">
         <v>54.8</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>57.191204</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>56.63954</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>53.8</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>58.898575</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30">
         <v>52.4</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>15:21:27</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31">
         <v>54.2</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>57.2497</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>56.139385</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>51.4</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>58.986053</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>51.1</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>15:21:28</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32">
         <v>51.9</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>55.549213</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>53.268833</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>51.4</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>56.02065</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32">
         <v>50.7</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>15:21:29</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33">
         <v>51.5</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>54.69643</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>54.16682</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>50.7</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>56.457436</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33">
         <v>52.1</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>15:21:30</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34">
         <v>52.5</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>53.518032</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>53.78528</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>51.6</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>55.862736</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34">
         <v>50.4</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>15:21:31</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35">
         <v>50.4</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>54.241974</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>54.02511</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35">
         <v>50.7</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35">
         <v>56.673893</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35">
         <v>50</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>15:21:32</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36">
         <v>50.7</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>53.143177</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>53.300274</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>50.4</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>55.99534</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36">
         <v>49.2</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>15:21:33</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37">
         <v>49.2</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>53.282036</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>51.946327</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>49.6</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37">
         <v>54.651035</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37">
         <v>49.1</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>15:21:34</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38">
         <v>49.8</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>52.543472</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>51.873745</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>49</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>54.305183</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38">
         <v>48.8</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>15:21:35</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39">
         <v>49.5</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>52.32016</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>51.43548</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>49.7</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>54.06913</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39">
         <v>50.5</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>15:21:36</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40">
         <v>52.3</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>51.4946</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>52.550945</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40">
         <v>51.3</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40">
         <v>54.582504</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40">
         <v>50.7</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>15:21:37</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41">
         <v>50.9</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>53.453953</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>54.640755</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>50.1</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
         <v>56.347763</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G41">
         <v>50.3</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>15:21:38</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42">
         <v>51.2</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>53.071594</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>53.0312</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42">
         <v>50.7</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42">
         <v>55.269352</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G42">
         <v>51.2</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>15:21:39</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43">
         <v>52.2</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>53.283485</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>54.809864</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43">
         <v>51.3</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>56.664776</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43">
         <v>50.5</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>15:21:40</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44">
         <v>51.4</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>54.63303</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>53.865204</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44">
         <v>50.8</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>56.29866</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44">
         <v>50.3</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>15:21:41</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45">
         <v>51.3</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>53.762035</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>52.924473</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>51.1</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>56.09458</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45">
         <v>51.5</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>15:21:42</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46">
         <v>52.1</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>52.463062</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>54.498466</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46">
         <v>50.6</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46">
         <v>59.440544</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G46">
         <v>50.6</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>15:21:43</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47">
         <v>50.5</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>53.84534</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>53.55356</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47">
         <v>49.4</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47">
         <v>55.822567</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47">
         <v>49</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>15:21:44</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48">
         <v>50</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>53.33423</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>52.087067</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48">
         <v>49</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48">
         <v>54.120266</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48">
         <v>49.8</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>15:21:45</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49">
         <v>50.2</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>52.028236</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49">
         <v>52.568848</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49">
         <v>49.2</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49">
         <v>54.458344</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49">
         <v>49.6</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>15:21:46</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50">
         <v>50.2</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>52.9255</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50">
         <v>52.652924</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50">
         <v>49.7</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50">
         <v>54.82685</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50">
         <v>49.3</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>15:21:47</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51">
         <v>50.3</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>52.55764</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>52.51383</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51">
         <v>49.3</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51">
         <v>54.865562</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G51">
         <v>49.4</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>15:21:48</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52">
         <v>49.3</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>53.071228</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52">
         <v>51.927803</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52">
         <v>48.2</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52">
         <v>54.50927</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G52">
         <v>48.2</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>15:21:49</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53">
         <v>49.1</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>51.69321</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53">
         <v>50.879158</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53">
         <v>48.7</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53">
         <v>53.373337</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G53">
         <v>50.5</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>15:21:50</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54">
         <v>51.6</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>51.43867</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54">
         <v>52.390697</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54">
         <v>52</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54">
         <v>54.474308</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G54">
         <v>51.9</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>15:21:51</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55">
         <v>52.4</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55">
         <v>53.69842</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>54.83838</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55">
         <v>51.8</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55">
         <v>57.725872</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G55">
         <v>49.9</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>15:21:52</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56">
         <v>50.4</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56">
         <v>55.55314</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56">
         <v>52.883625</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56">
         <v>50.7</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56">
         <v>55.798344</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G56">
         <v>49.9</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>15:21:53</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57">
         <v>51.6</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57">
         <v>52.78049</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57">
         <v>53.38847</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57">
         <v>50.8</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57">
         <v>56.211277</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G57">
         <v>52.4</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>15:21:54</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58">
         <v>53.7</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58">
         <v>53.64889</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58">
         <v>55.06299</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58">
         <v>52.2</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58">
         <v>56.485683</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G58">
         <v>52</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>15:21:55</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59">
         <v>52.5</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59">
         <v>57.03024</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59">
         <v>55.29999</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59">
         <v>52.1</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59">
         <v>57.591255</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G59">
         <v>52.2</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>15:21:56</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60">
         <v>52.4</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60">
         <v>55.7344</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60">
         <v>55.132504</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60">
         <v>51.6</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60">
         <v>57.47278</v>
       </c>
-      <c r="G60" t="n">
+      <c r="G60">
         <v>52.7</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>15:21:57</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61">
         <v>54.1</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61">
         <v>56.032677</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>54.800064</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61">
         <v>52</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61">
         <v>59.287563</v>
       </c>
-      <c r="G61" t="n">
+      <c r="G61">
         <v>52.8</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>15:21:58</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62">
         <v>54</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62">
         <v>56.805553</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62">
         <v>55.76985</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62">
         <v>52.8</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62">
         <v>58.34252</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G62">
         <v>53.7</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>15:21:59</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>68</v>
+      </c>
+      <c r="B63">
         <v>54.4</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63">
         <v>59.406467</v>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="n">
+      <c r="E63">
         <v>52.9</v>
       </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>15:22:00</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64">
         <v>53.8</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64">
         <v>59.134624</v>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="n">
+      <c r="E64">
         <v>56.3</v>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>15:22:01</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65">
         <v>61.2</v>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="n">
+      <c r="E65">
         <v>59.5</v>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>15:22:02</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>15:22:03</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>15:22:04</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>15:22:05</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>15:22:06</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>75</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>